--- a/MasterData.xlsx
+++ b/MasterData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727B258B-BD6E-462A-B2DD-FA4D8F4386B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C8147-1530-4E24-8E06-50DD4E104E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FBEDCA38-5975-469B-BEBF-0C675824030B}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>name</t>
   </si>
@@ -59,16 +59,13 @@
     <t>Harvesting</t>
   </si>
   <si>
-    <t>sowing.png</t>
-  </si>
-  <si>
     <t>Stage for sowing seeds</t>
   </si>
   <si>
     <t>Final harvesting stage</t>
   </si>
   <si>
-    <t>harvest.jpg</t>
+    <t>static/images/nudges/default.png</t>
   </si>
 </sst>
 </file>
@@ -477,7 +474,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
     <col min="3" max="3" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -497,10 +494,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -508,10 +505,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
